--- a/results/plots/random_forest/RF Model Comparison.xlsx
+++ b/results/plots/random_forest/RF Model Comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/75590eaecb4bf32b/Desktop/Python/Thesis_xyz/results/plots/random_forest/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FFFAE27-9BD5-4A97-9F8E-2C2F627B5A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="219" documentId="8_{3FFFAE27-9BD5-4A97-9F8E-2C2F627B5A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F9B5BA3-3097-4883-A2E8-601A13A010B7}"/>
   <bookViews>
-    <workbookView xWindow="62280" yWindow="315" windowWidth="21600" windowHeight="11235" xr2:uid="{248DD4FA-FB47-4AC4-A0A2-0D6589504343}"/>
+    <workbookView xWindow="28680" yWindow="-1965" windowWidth="29040" windowHeight="15720" xr2:uid="{248DD4FA-FB47-4AC4-A0A2-0D6589504343}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>Q1 Avg. RD</t>
-  </si>
-  <si>
-    <t>Depth</t>
   </si>
   <si>
     <t>Yearly</t>
@@ -112,6 +109,9 @@
   <si>
     <t>Geo Score</t>
   </si>
+  <si>
+    <t>Depth of RF</t>
+  </si>
 </sst>
 </file>
 
@@ -137,12 +137,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -158,11 +164,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -204,9 +214,12 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{80E4AF34-3C5D-4173-942F-03A3F6502C94}" name="Table1" displayName="Table1" ref="B2:U30" totalsRowShown="0">
   <autoFilter ref="B2:U30" xr:uid="{80E4AF34-3C5D-4173-942F-03A3F6502C94}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:U30">
+    <sortCondition descending="1" ref="R2:R30"/>
+  </sortState>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{AF1AE090-941F-4DED-9BC2-4D6FAE032D6D}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{564C3F77-9A8A-410A-8420-A0E5335EBEC7}" name="Depth"/>
+    <tableColumn id="2" xr3:uid="{564C3F77-9A8A-410A-8420-A0E5335EBEC7}" name="Depth of RF"/>
     <tableColumn id="3" xr3:uid="{1EBA3815-00BE-4EA1-9893-1D915F493B25}" name="Count"/>
     <tableColumn id="4" xr3:uid="{162C14A2-3DD3-4841-9A65-A1155C8AB07A}" name="Avg. DD%"/>
     <tableColumn id="5" xr3:uid="{299CD6F2-F1AE-41AE-9823-DFD52F5145EF}" name="Avg. DtT"/>
@@ -553,7 +566,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" customWidth="1"/>
     <col min="5" max="5" width="11.21875" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="9.5546875" customWidth="1"/>
@@ -573,19 +587,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
         <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -600,165 +614,165 @@
         <v>4</v>
       </c>
       <c r="L2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" t="s">
         <v>10</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>16</v>
       </c>
-      <c r="N2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>17</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>19</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>20</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>21</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>22</v>
       </c>
-      <c r="U2" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4">
         <v>1</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="4">
         <v>35</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="5">
         <v>0.123</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="4">
         <v>134</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="4">
         <v>94</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="4">
         <v>8</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="5">
         <v>0.27300000000000002</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="4">
         <v>497</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="4">
         <v>305</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="6">
         <v>5.1000000000000004E-4</v>
       </c>
-      <c r="M3" s="1">
+      <c r="M3" s="7">
         <v>18.86</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="5">
         <f>(1 + M3)^(1/28) - 1</f>
         <v>0.11264443877371599</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="4">
         <v>0.28639999999999999</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="4">
         <v>8.2199999999999995E-2</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="4">
         <v>0.246</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="4">
         <v>1.09E-2</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="4">
         <v>7.9200000000000007E-2</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="4">
         <v>0.5948</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="4">
         <v>0.29189999999999999</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2">
-        <v>0.14599999999999999</v>
+        <v>0.121</v>
       </c>
       <c r="F4">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="G4">
-        <v>192</v>
+        <v>87</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I4" s="2">
-        <v>0.34399999999999997</v>
+        <v>0.255</v>
       </c>
       <c r="J4">
-        <v>297</v>
+        <v>439</v>
       </c>
       <c r="K4">
-        <v>681</v>
+        <v>258</v>
       </c>
       <c r="L4" s="3">
-        <v>4.8999999999999998E-4</v>
+        <v>5.1999999999999995E-4</v>
       </c>
       <c r="M4" s="1">
-        <v>15.58</v>
+        <v>19.62</v>
       </c>
       <c r="N4" s="2">
-        <f t="shared" ref="N4:N6" si="0">(1 + M4)^(1/28) - 1</f>
-        <v>0.10549451013525535</v>
+        <f>(1 + M4)^(1/28) - 1</f>
+        <v>0.11413772741746597</v>
       </c>
       <c r="O4">
-        <v>0.28870000000000001</v>
+        <v>0.28689999999999999</v>
       </c>
       <c r="P4">
-        <v>8.3400000000000002E-2</v>
+        <v>8.2699999999999996E-2</v>
       </c>
       <c r="Q4">
-        <v>0.2495</v>
+        <v>0.24479999999999999</v>
       </c>
       <c r="R4">
-        <v>-3.5000000000000001E-3</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="S4">
-        <v>-1.0999999999999999E-2</v>
+        <v>6.6400000000000001E-2</v>
       </c>
       <c r="T4">
-        <v>0.58069999999999999</v>
+        <v>0.57120000000000004</v>
       </c>
       <c r="U4">
-        <v>0.1716</v>
+        <v>0.38729999999999998</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -794,7 +808,7 @@
         <v>20.79</v>
       </c>
       <c r="N5" s="2">
-        <f t="shared" si="0"/>
+        <f>(1 + M5)^(1/28) - 1</f>
         <v>0.11633592502082024</v>
       </c>
       <c r="O5">
@@ -821,7 +835,7 @@
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -857,7 +871,7 @@
         <v>18.41</v>
       </c>
       <c r="N6" s="2">
-        <f t="shared" si="0"/>
+        <f>(1 + M6)^(1/28) - 1</f>
         <v>0.11173406181761969</v>
       </c>
       <c r="O6">
@@ -884,774 +898,821 @@
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2">
-        <v>0.121</v>
+        <v>0.13</v>
       </c>
       <c r="F7">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="G7">
-        <v>87</v>
+        <v>151</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I7" s="2">
-        <v>0.255</v>
+        <v>0.307</v>
       </c>
       <c r="J7">
-        <v>439</v>
+        <v>250</v>
       </c>
       <c r="K7">
-        <v>258</v>
+        <v>552</v>
       </c>
       <c r="L7" s="3">
-        <v>5.1999999999999995E-4</v>
+        <v>5.1000000000000004E-4</v>
       </c>
       <c r="M7" s="1">
-        <v>19.62</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="N7" s="2">
-        <f t="shared" ref="N7:N10" si="1">(1 + M7)^(1/28) - 1</f>
-        <v>0.11413772741746597</v>
+        <f>(1 + M7)^(1/28) - 1</f>
+        <v>0.11119874461468071</v>
       </c>
       <c r="O7">
-        <v>0.28689999999999999</v>
+        <v>0.28849999999999998</v>
       </c>
       <c r="P7">
-        <v>8.2699999999999996E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
       <c r="Q7">
-        <v>0.24479999999999999</v>
+        <v>0.24979999999999999</v>
       </c>
       <c r="R7">
-        <v>4.8999999999999998E-3</v>
+        <v>-2E-3</v>
       </c>
       <c r="S7">
-        <v>6.6400000000000001E-2</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="T7">
-        <v>0.57120000000000004</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="U7">
-        <v>0.38729999999999998</v>
+        <v>0.17949999999999999</v>
       </c>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2">
-        <v>0.14199999999999999</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="F8">
         <v>89</v>
       </c>
       <c r="G8">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H8">
         <v>7</v>
       </c>
       <c r="I8" s="2">
-        <v>0.34100000000000003</v>
+        <v>0.34399999999999997</v>
       </c>
       <c r="J8">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="K8">
-        <v>652</v>
+        <v>681</v>
       </c>
       <c r="L8" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>4.8999999999999998E-4</v>
       </c>
       <c r="M8" s="1">
-        <v>16.34</v>
+        <v>15.58</v>
       </c>
       <c r="N8" s="2">
-        <f t="shared" si="1"/>
-        <v>0.10726546144481341</v>
+        <f>(1 + M8)^(1/28) - 1</f>
+        <v>0.10549451013525535</v>
       </c>
       <c r="O8">
-        <v>0.2898</v>
+        <v>0.28870000000000001</v>
       </c>
       <c r="P8">
-        <v>8.4199999999999997E-2</v>
+        <v>8.3400000000000002E-2</v>
       </c>
       <c r="Q8">
-        <v>0.24979999999999999</v>
+        <v>0.2495</v>
       </c>
       <c r="R8">
-        <v>-1.2500000000000001E-2</v>
+        <v>-3.5000000000000001E-3</v>
       </c>
       <c r="S8">
-        <v>-1.61E-2</v>
+        <v>-1.0999999999999999E-2</v>
       </c>
       <c r="T8">
-        <v>0.55149999999999999</v>
+        <v>0.58069999999999999</v>
       </c>
       <c r="U8">
-        <v>0.32650000000000001</v>
+        <v>0.1716</v>
       </c>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2">
-        <v>0.13300000000000001</v>
+        <v>0.129</v>
       </c>
       <c r="F9">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G9">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="2">
-        <v>0.31</v>
+        <v>0.29599999999999999</v>
       </c>
       <c r="J9">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="K9">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="L9" s="3">
-        <v>5.4000000000000001E-4</v>
+        <v>5.1999999999999995E-4</v>
       </c>
       <c r="M9" s="1">
-        <v>22.31</v>
+        <v>20.09</v>
       </c>
       <c r="N9" s="2">
-        <f t="shared" si="1"/>
-        <v>0.11902759295446086</v>
+        <f>(1 + M9)^(1/28) - 1</f>
+        <v>0.11503487045603955</v>
       </c>
       <c r="O9">
-        <v>0.28849999999999998</v>
+        <v>0.2878</v>
       </c>
       <c r="P9">
         <v>8.3400000000000002E-2</v>
       </c>
       <c r="Q9">
-        <v>0.24959999999999999</v>
+        <v>0.24460000000000001</v>
       </c>
       <c r="R9">
-        <v>-0.03</v>
+        <v>-3.8999999999999998E-3</v>
       </c>
       <c r="S9">
-        <v>4.7800000000000002E-2</v>
+        <v>6.88E-2</v>
       </c>
       <c r="T9">
-        <v>0.53169999999999995</v>
+        <v>0.56669999999999998</v>
       </c>
       <c r="U9">
-        <v>0.34229999999999999</v>
+        <v>0.4244</v>
       </c>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2">
         <v>0.13</v>
       </c>
       <c r="F10">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G10">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H10">
         <v>8</v>
       </c>
       <c r="I10" s="2">
-        <v>0.307</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="J10">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="K10">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="L10" s="3">
         <v>5.1000000000000004E-4</v>
       </c>
       <c r="M10" s="1">
-        <v>18.149999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="N10" s="2">
-        <f t="shared" si="1"/>
-        <v>0.11119874461468071</v>
+        <f>(1 + M10)^(1/28) - 1</f>
+        <v>0.11130223233281478</v>
       </c>
       <c r="O10">
-        <v>0.28849999999999998</v>
+        <v>0.28889999999999999</v>
       </c>
       <c r="P10">
-        <v>8.3299999999999999E-2</v>
+        <v>8.3500000000000005E-2</v>
       </c>
       <c r="Q10">
-        <v>0.24979999999999999</v>
+        <v>0.25009999999999999</v>
       </c>
       <c r="R10">
-        <v>-2E-3</v>
+        <v>-4.7000000000000002E-3</v>
       </c>
       <c r="S10">
-        <v>1.5699999999999999E-2</v>
+        <v>1.24E-2</v>
       </c>
       <c r="T10">
-        <v>0.54500000000000004</v>
+        <v>0.53820000000000001</v>
       </c>
       <c r="U10">
-        <v>0.17949999999999999</v>
+        <v>0.27529999999999999</v>
       </c>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E11" s="2">
-        <v>0.129</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="F11">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G11">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I11" s="2">
-        <v>0.29599999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="J11">
-        <v>232</v>
+        <v>285</v>
       </c>
       <c r="K11">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="L11" s="3">
-        <v>5.1999999999999995E-4</v>
+        <v>5.5000000000000003E-4</v>
       </c>
       <c r="M11" s="1">
-        <v>20.09</v>
+        <v>23.23</v>
       </c>
       <c r="N11" s="2">
-        <f t="shared" ref="N11:N18" si="2">(1 + M11)^(1/28) - 1</f>
-        <v>0.11503487045603955</v>
+        <f>(1 + M11)^(1/28) - 1</f>
+        <v>0.12057568174927447</v>
       </c>
       <c r="O11">
-        <v>0.2878</v>
+        <v>0.28910000000000002</v>
       </c>
       <c r="P11">
-        <v>8.3400000000000002E-2</v>
+        <v>8.3699999999999997E-2</v>
       </c>
       <c r="Q11">
-        <v>0.24460000000000001</v>
+        <v>0.24979999999999999</v>
       </c>
       <c r="R11">
-        <v>-3.8999999999999998E-3</v>
+        <v>-7.4999999999999997E-3</v>
       </c>
       <c r="S11">
-        <v>6.88E-2</v>
+        <v>4.9299999999999997E-2</v>
       </c>
       <c r="T11">
-        <v>0.56669999999999998</v>
+        <v>0.52110000000000001</v>
       </c>
       <c r="U11">
-        <v>0.4244</v>
+        <v>0.38779999999999998</v>
       </c>
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2">
-        <v>0.13500000000000001</v>
+        <v>0.124</v>
       </c>
       <c r="F12">
         <v>76</v>
       </c>
       <c r="G12">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="H12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="2">
-        <v>0.312</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="J12">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="K12">
-        <v>583</v>
+        <v>457</v>
       </c>
       <c r="L12" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>5.1000000000000004E-4</v>
       </c>
       <c r="M12" s="1">
-        <v>17.28</v>
+        <v>18.79</v>
       </c>
       <c r="N12" s="2">
-        <f t="shared" si="2"/>
-        <v>0.1093550846367628</v>
+        <f>(1 + M12)^(1/28) - 1</f>
+        <v>0.11250413922221303</v>
       </c>
       <c r="O12">
-        <v>0.29099999999999998</v>
+        <v>0.2898</v>
       </c>
       <c r="P12">
-        <v>8.4900000000000003E-2</v>
+        <v>8.4099999999999994E-2</v>
       </c>
       <c r="Q12">
-        <v>0.25019999999999998</v>
+        <v>0.25059999999999999</v>
       </c>
       <c r="R12">
-        <v>-2.1600000000000001E-2</v>
+        <v>-1.14E-2</v>
       </c>
       <c r="S12">
-        <v>-8.8999999999999999E-3</v>
+        <v>1.04E-2</v>
       </c>
       <c r="T12">
-        <v>0.54710000000000003</v>
+        <v>0.53120000000000001</v>
       </c>
       <c r="U12">
-        <v>0.3886</v>
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2">
-        <v>0.13100000000000001</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="F13">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G13">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="H13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I13" s="2">
-        <v>0.30499999999999999</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="J13">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="K13">
-        <v>466</v>
+        <v>652</v>
       </c>
       <c r="L13" s="3">
-        <v>5.5000000000000003E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="M13" s="1">
-        <v>23.23</v>
+        <v>16.34</v>
       </c>
       <c r="N13" s="2">
-        <f t="shared" si="2"/>
-        <v>0.12057568174927447</v>
+        <f>(1 + M13)^(1/28) - 1</f>
+        <v>0.10726546144481341</v>
       </c>
       <c r="O13">
-        <v>0.28910000000000002</v>
+        <v>0.2898</v>
       </c>
       <c r="P13">
-        <v>8.3699999999999997E-2</v>
+        <v>8.4199999999999997E-2</v>
       </c>
       <c r="Q13">
         <v>0.24979999999999999</v>
       </c>
       <c r="R13">
-        <v>-7.4999999999999997E-3</v>
+        <v>-1.2500000000000001E-2</v>
       </c>
       <c r="S13">
-        <v>4.9299999999999997E-2</v>
+        <v>-1.61E-2</v>
       </c>
       <c r="T13">
-        <v>0.52110000000000001</v>
+        <v>0.55149999999999999</v>
       </c>
       <c r="U13">
-        <v>0.38779999999999998</v>
+        <v>0.32650000000000001</v>
       </c>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>36</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.127</v>
+      </c>
+      <c r="F14">
+        <v>82</v>
+      </c>
+      <c r="G14">
+        <v>130</v>
+      </c>
+      <c r="H14">
         <v>9</v>
       </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <v>34</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="F14">
-        <v>80</v>
-      </c>
-      <c r="G14">
-        <v>155</v>
-      </c>
-      <c r="H14">
-        <v>8</v>
-      </c>
       <c r="I14" s="2">
-        <v>0.30399999999999999</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="J14">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="K14">
-        <v>542</v>
+        <v>413</v>
       </c>
       <c r="L14" s="3">
-        <v>5.1000000000000004E-4</v>
+        <v>5.5000000000000003E-4</v>
       </c>
       <c r="M14" s="1">
-        <v>18.2</v>
+        <v>23.82</v>
       </c>
       <c r="N14" s="2">
-        <f t="shared" si="2"/>
-        <v>0.11130223233281478</v>
+        <f>(1 + M14)^(1/28) - 1</f>
+        <v>0.12153891994517685</v>
       </c>
       <c r="O14">
-        <v>0.28889999999999999</v>
+        <v>0.29049999999999998</v>
       </c>
       <c r="P14">
-        <v>8.3500000000000005E-2</v>
+        <v>8.4599999999999995E-2</v>
       </c>
       <c r="Q14">
-        <v>0.25009999999999999</v>
+        <v>0.2505</v>
       </c>
       <c r="R14">
-        <v>-4.7000000000000002E-3</v>
+        <v>-1.7899999999999999E-2</v>
       </c>
       <c r="S14">
-        <v>1.24E-2</v>
+        <v>4.2299999999999997E-2</v>
       </c>
       <c r="T14">
-        <v>0.53820000000000001</v>
+        <v>0.51970000000000005</v>
       </c>
       <c r="U14">
-        <v>0.27529999999999999</v>
+        <v>0.41880000000000001</v>
       </c>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E15" s="2">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="F15">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G15">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I15" s="2">
-        <v>0.27400000000000002</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="J15">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="K15">
-        <v>392</v>
+        <v>445</v>
       </c>
       <c r="L15" s="3">
-        <v>5.1999999999999995E-4</v>
+        <v>5.1000000000000004E-4</v>
       </c>
       <c r="M15" s="1">
-        <v>20.36</v>
+        <v>19.03</v>
       </c>
       <c r="N15" s="2">
-        <f t="shared" si="2"/>
-        <v>0.11554157056568926</v>
+        <f>(1 + M15)^(1/28) - 1</f>
+        <v>0.11298319086405839</v>
       </c>
       <c r="O15">
-        <v>0.29020000000000001</v>
+        <v>0.29110000000000003</v>
       </c>
       <c r="P15">
-        <v>8.5099999999999995E-2</v>
+        <v>8.4900000000000003E-2</v>
       </c>
       <c r="Q15">
-        <v>0.24610000000000001</v>
+        <v>0.2515</v>
       </c>
       <c r="R15">
-        <v>-2.4199999999999999E-2</v>
+        <v>-2.1000000000000001E-2</v>
       </c>
       <c r="S15">
-        <v>7.0499999999999993E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="T15">
-        <v>0.55189999999999995</v>
+        <v>0.52129999999999999</v>
       </c>
       <c r="U15">
-        <v>0.43440000000000001</v>
+        <v>0.39019999999999999</v>
       </c>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2">
-        <v>0.13200000000000001</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="F16">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G16">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H16">
         <v>8</v>
       </c>
       <c r="I16" s="2">
-        <v>0.30399999999999999</v>
+        <v>0.312</v>
       </c>
       <c r="J16">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="K16">
-        <v>552</v>
+        <v>583</v>
       </c>
       <c r="L16" s="3">
-        <v>5.1000000000000004E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="M16" s="1">
-        <v>19.100000000000001</v>
+        <v>17.28</v>
       </c>
       <c r="N16" s="2">
-        <f t="shared" si="2"/>
-        <v>0.11312187185817946</v>
+        <f>(1 + M16)^(1/28) - 1</f>
+        <v>0.1093550846367628</v>
       </c>
       <c r="O16">
-        <v>0.29260000000000003</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="P16">
-        <v>8.5900000000000004E-2</v>
+        <v>8.4900000000000003E-2</v>
       </c>
       <c r="Q16">
-        <v>0.25069999999999998</v>
+        <v>0.25019999999999998</v>
       </c>
       <c r="R16">
-        <v>-3.3599999999999998E-2</v>
+        <v>-2.1600000000000001E-2</v>
       </c>
       <c r="S16">
-        <v>2.9999999999999997E-4</v>
+        <v>-8.8999999999999999E-3</v>
       </c>
       <c r="T16">
-        <v>0.54079999999999995</v>
+        <v>0.54710000000000003</v>
       </c>
       <c r="U16">
-        <v>0.40529999999999999</v>
+        <v>0.3886</v>
       </c>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C17">
         <v>5</v>
       </c>
       <c r="D17">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E17" s="2">
-        <v>0.127</v>
+        <v>0.125</v>
       </c>
       <c r="F17">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G17">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="H17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I17" s="2">
-        <v>0.27600000000000002</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="J17">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="K17">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="L17" s="3">
-        <v>5.5000000000000003E-4</v>
+        <v>5.1999999999999995E-4</v>
       </c>
       <c r="M17" s="1">
-        <v>23.82</v>
+        <v>20.36</v>
       </c>
       <c r="N17" s="2">
-        <f t="shared" si="2"/>
-        <v>0.12153891994517685</v>
+        <f>(1 + M17)^(1/28) - 1</f>
+        <v>0.11554157056568926</v>
       </c>
       <c r="O17">
-        <v>0.29049999999999998</v>
+        <v>0.29020000000000001</v>
       </c>
       <c r="P17">
-        <v>8.4599999999999995E-2</v>
+        <v>8.5099999999999995E-2</v>
       </c>
       <c r="Q17">
-        <v>0.2505</v>
+        <v>0.24610000000000001</v>
       </c>
       <c r="R17">
-        <v>-1.7899999999999999E-2</v>
+        <v>-2.4199999999999999E-2</v>
       </c>
       <c r="S17">
-        <v>4.2299999999999997E-2</v>
+        <v>7.0499999999999993E-2</v>
       </c>
       <c r="T17">
-        <v>0.51970000000000005</v>
+        <v>0.55189999999999995</v>
       </c>
       <c r="U17">
-        <v>0.41880000000000001</v>
+        <v>0.43440000000000001</v>
       </c>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D18">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2">
-        <v>0.124</v>
+        <v>0.12</v>
       </c>
       <c r="F18">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G18">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="H18">
         <v>9</v>
       </c>
       <c r="I18" s="2">
-        <v>0.27600000000000002</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="J18">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K18">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="L18" s="3">
-        <v>5.1000000000000004E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="M18" s="1">
-        <v>18.79</v>
+        <v>18.02</v>
       </c>
       <c r="N18" s="2">
-        <f t="shared" si="2"/>
-        <v>0.11250413922221303</v>
+        <f>(1 + M18)^(1/28) - 1</f>
+        <v>0.11092845226548476</v>
       </c>
       <c r="O18">
-        <v>0.2898</v>
+        <v>0.2918</v>
       </c>
       <c r="P18">
-        <v>8.4099999999999994E-2</v>
+        <v>8.5300000000000001E-2</v>
       </c>
       <c r="Q18">
-        <v>0.25059999999999999</v>
+        <v>0.252</v>
       </c>
       <c r="R18">
-        <v>-1.14E-2</v>
+        <v>-2.63E-2</v>
       </c>
       <c r="S18">
-        <v>1.04E-2</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="T18">
-        <v>0.53120000000000001</v>
+        <v>0.52059999999999995</v>
       </c>
       <c r="U18">
-        <v>0.35289999999999999</v>
+        <v>0.4042</v>
       </c>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="D19">
+        <v>39</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="F19">
+        <v>71</v>
+      </c>
+      <c r="G19">
+        <v>127</v>
+      </c>
+      <c r="H19">
+        <v>9</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="J19">
+        <v>218</v>
+      </c>
+      <c r="K19">
+        <v>441</v>
+      </c>
+      <c r="L19" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="M19" s="1">
+        <v>18.170000000000002</v>
+      </c>
       <c r="N19" s="2">
-        <f t="shared" ref="N19:N30" si="3">(1 + M19)^(1/28) - 1</f>
-        <v>0</v>
+        <f>(1 + M19)^(1/28) - 1</f>
+        <v>0.11124017093284899</v>
+      </c>
+      <c r="O19">
+        <v>0.2923</v>
+      </c>
+      <c r="P19">
+        <v>8.5599999999999996E-2</v>
+      </c>
+      <c r="Q19">
+        <v>0.25230000000000002</v>
+      </c>
+      <c r="R19">
+        <v>-2.9700000000000001E-2</v>
+      </c>
+      <c r="S19">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="T19">
+        <v>0.51680000000000004</v>
+      </c>
+      <c r="U19">
+        <v>0.41360000000000002</v>
       </c>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.3">
@@ -1659,54 +1720,251 @@
         <v>7</v>
       </c>
       <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>35</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="F20">
+        <v>89</v>
+      </c>
+      <c r="G20">
+        <v>134</v>
+      </c>
+      <c r="H20">
         <v>8</v>
       </c>
-      <c r="E20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="1"/>
+      <c r="I20" s="2">
+        <v>0.31</v>
+      </c>
+      <c r="J20">
+        <v>286</v>
+      </c>
+      <c r="K20">
+        <v>479</v>
+      </c>
+      <c r="L20" s="3">
+        <v>5.4000000000000001E-4</v>
+      </c>
+      <c r="M20" s="1">
+        <v>22.31</v>
+      </c>
       <c r="N20" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>(1 + M20)^(1/28) - 1</f>
+        <v>0.11902759295446086</v>
+      </c>
+      <c r="O20">
+        <v>0.28849999999999998</v>
+      </c>
+      <c r="P20">
+        <v>8.3400000000000002E-2</v>
+      </c>
+      <c r="Q20">
+        <v>0.24959999999999999</v>
+      </c>
+      <c r="R20">
+        <v>-0.03</v>
+      </c>
+      <c r="S20">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="T20">
+        <v>0.53169999999999995</v>
+      </c>
+      <c r="U20">
+        <v>0.34229999999999999</v>
       </c>
     </row>
     <row r="21" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>8</v>
       </c>
-      <c r="I21" s="2"/>
-      <c r="N21">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="D21">
+        <v>36</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.124</v>
+      </c>
+      <c r="F21">
+        <v>83</v>
+      </c>
+      <c r="G21">
+        <v>127</v>
+      </c>
+      <c r="H21">
+        <v>9</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="J21">
+        <v>240</v>
+      </c>
+      <c r="K21">
+        <v>405</v>
+      </c>
+      <c r="L21" s="3">
+        <v>5.4000000000000001E-4</v>
+      </c>
+      <c r="M21" s="1">
+        <v>23.51</v>
+      </c>
+      <c r="N21" s="2">
+        <f>(1 + M21)^(1/28) - 1</f>
+        <v>0.12103559884182968</v>
+      </c>
+      <c r="O21">
+        <v>0.2923</v>
+      </c>
+      <c r="P21">
+        <v>8.5699999999999998E-2</v>
+      </c>
+      <c r="Q21">
+        <v>0.25159999999999999</v>
+      </c>
+      <c r="R21">
+        <v>-3.15E-2</v>
+      </c>
+      <c r="S21">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="T21">
+        <v>0.51990000000000003</v>
+      </c>
+      <c r="U21">
+        <v>0.43819999999999998</v>
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22">
+        <v>35</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="F22">
+        <v>73</v>
+      </c>
+      <c r="G22">
+        <v>153</v>
+      </c>
+      <c r="H22">
         <v>8</v>
       </c>
-      <c r="I22" s="2"/>
-      <c r="N22">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="I22" s="2">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="J22">
+        <v>227</v>
+      </c>
+      <c r="K22">
+        <v>552</v>
+      </c>
+      <c r="L22" s="3">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="M22" s="1">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="N22" s="2">
+        <f>(1 + M22)^(1/28) - 1</f>
+        <v>0.11312187185817946</v>
+      </c>
+      <c r="O22">
+        <v>0.29260000000000003</v>
+      </c>
+      <c r="P22">
+        <v>8.5900000000000004E-2</v>
+      </c>
+      <c r="Q22">
+        <v>0.25069999999999998</v>
+      </c>
+      <c r="R22">
+        <v>-3.3599999999999998E-2</v>
+      </c>
+      <c r="S22">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="T22">
+        <v>0.54079999999999995</v>
+      </c>
+      <c r="U22">
+        <v>0.40529999999999999</v>
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C23">
         <v>10</v>
       </c>
-      <c r="I23" s="2"/>
-      <c r="N23">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="D23">
+        <v>37</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.122</v>
+      </c>
+      <c r="F23">
+        <v>83</v>
+      </c>
+      <c r="G23">
+        <v>123</v>
+      </c>
+      <c r="H23">
+        <v>9</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="J23">
+        <v>240</v>
+      </c>
+      <c r="K23">
+        <v>396</v>
+      </c>
+      <c r="L23" s="3">
+        <v>5.4000000000000001E-4</v>
+      </c>
+      <c r="M23" s="1">
+        <v>22.89</v>
+      </c>
+      <c r="N23" s="2">
+        <f>(1 + M23)^(1/28) - 1</f>
+        <v>0.12001027095675987</v>
+      </c>
+      <c r="O23">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="P23">
+        <v>8.6199999999999999E-2</v>
+      </c>
+      <c r="Q23">
+        <v>0.25230000000000002</v>
+      </c>
+      <c r="R23">
+        <v>-3.7100000000000001E-2</v>
+      </c>
+      <c r="S23">
+        <v>3.8800000000000001E-2</v>
+      </c>
+      <c r="T23">
+        <v>0.5212</v>
+      </c>
+      <c r="U23">
+        <v>0.44309999999999999</v>
       </c>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.3">
@@ -1714,90 +1972,440 @@
         <v>7</v>
       </c>
       <c r="C24">
-        <v>10</v>
-      </c>
-      <c r="I24" s="2"/>
-      <c r="N24">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="D24">
+        <v>38</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="F24">
+        <v>81</v>
+      </c>
+      <c r="G24">
+        <v>117</v>
+      </c>
+      <c r="H24">
+        <v>9</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="J24">
+        <v>240</v>
+      </c>
+      <c r="K24">
+        <v>390</v>
+      </c>
+      <c r="L24" s="3">
+        <v>5.2999999999999998E-4</v>
+      </c>
+      <c r="M24" s="1">
+        <v>22.45</v>
+      </c>
+      <c r="N24" s="2">
+        <f>(1 + M24)^(1/28) - 1</f>
+        <v>0.11926693226207696</v>
+      </c>
+      <c r="O24">
+        <v>0.29370000000000002</v>
+      </c>
+      <c r="P24">
+        <v>8.6599999999999996E-2</v>
+      </c>
+      <c r="Q24">
+        <v>0.25269999999999998</v>
+      </c>
+      <c r="R24">
+        <v>-4.2200000000000001E-2</v>
+      </c>
+      <c r="S24">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="T24">
+        <v>0.52290000000000003</v>
+      </c>
+      <c r="U24">
+        <v>0.4496</v>
       </c>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25">
         <v>8</v>
       </c>
-      <c r="C25">
-        <v>10</v>
-      </c>
-      <c r="I25" s="2"/>
-      <c r="N25">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="D25">
+        <v>38</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0.126</v>
+      </c>
+      <c r="F25">
+        <v>77</v>
+      </c>
+      <c r="G25">
+        <v>124</v>
+      </c>
+      <c r="H25">
+        <v>9</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="J25">
+        <v>229</v>
+      </c>
+      <c r="K25">
+        <v>429</v>
+      </c>
+      <c r="L25" s="3">
+        <v>5.1999999999999995E-4</v>
+      </c>
+      <c r="M25" s="1">
+        <v>20.13</v>
+      </c>
+      <c r="N25" s="2">
+        <f>(1 + M25)^(1/28) - 1</f>
+        <v>0.11511033049080166</v>
+      </c>
+      <c r="O25">
+        <v>0.29249999999999998</v>
+      </c>
+      <c r="P25">
+        <v>8.6699999999999999E-2</v>
+      </c>
+      <c r="Q25">
+        <v>0.24779999999999999</v>
+      </c>
+      <c r="R25">
+        <v>-4.3200000000000002E-2</v>
+      </c>
+      <c r="S25">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="T25">
+        <v>0.53610000000000002</v>
+      </c>
+      <c r="U25">
+        <v>0.42259999999999998</v>
       </c>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>8</v>
+      </c>
+      <c r="D26">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.129</v>
+      </c>
+      <c r="F26">
+        <v>72</v>
+      </c>
+      <c r="G26">
+        <v>148</v>
+      </c>
+      <c r="H26">
         <v>9</v>
       </c>
-      <c r="C26">
-        <v>10</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="N26">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="I26" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J26">
+        <v>206</v>
+      </c>
+      <c r="K26">
+        <v>476</v>
+      </c>
+      <c r="L26" s="3">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="M26" s="1">
+        <v>19.61</v>
+      </c>
+      <c r="N26" s="2">
+        <f>(1 + M26)^(1/28) - 1</f>
+        <v>0.11411842579766041</v>
+      </c>
+      <c r="O26">
+        <v>0.29470000000000002</v>
+      </c>
+      <c r="P26">
+        <v>8.7300000000000003E-2</v>
+      </c>
+      <c r="Q26">
+        <v>0.25190000000000001</v>
+      </c>
+      <c r="R26">
+        <v>-4.9700000000000001E-2</v>
+      </c>
+      <c r="S26">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="T26">
+        <v>0.53339999999999999</v>
+      </c>
+      <c r="U26">
+        <v>0.41570000000000001</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27">
-        <v>20</v>
-      </c>
-      <c r="I27" s="2"/>
-      <c r="N27">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="D27">
+        <v>39</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.124</v>
+      </c>
+      <c r="F27">
+        <v>76</v>
+      </c>
+      <c r="G27">
+        <v>121</v>
+      </c>
+      <c r="H27">
+        <v>9</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="J27">
+        <v>229</v>
+      </c>
+      <c r="K27">
+        <v>430</v>
+      </c>
+      <c r="L27" s="3">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="M27" s="1">
+        <v>19.82</v>
+      </c>
+      <c r="N27" s="2">
+        <f>(1 + M27)^(1/28) - 1</f>
+        <v>0.11452187608085684</v>
+      </c>
+      <c r="O27">
+        <v>0.29370000000000002</v>
+      </c>
+      <c r="P27">
+        <v>8.7400000000000005E-2</v>
+      </c>
+      <c r="Q27">
+        <v>0.24859999999999999</v>
+      </c>
+      <c r="R27">
+        <v>-5.1799999999999999E-2</v>
+      </c>
+      <c r="S27">
+        <v>6.8599999999999994E-2</v>
+      </c>
+      <c r="T27">
+        <v>0.52839999999999998</v>
+      </c>
+      <c r="U27">
+        <v>0.4148</v>
       </c>
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28">
-        <v>20</v>
-      </c>
-      <c r="I28" s="2"/>
-      <c r="N28">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="D28">
+        <v>36</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.129</v>
+      </c>
+      <c r="F28">
+        <v>71</v>
+      </c>
+      <c r="G28">
+        <v>148</v>
+      </c>
+      <c r="H28">
+        <v>9</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J28">
+        <v>200</v>
+      </c>
+      <c r="K28">
+        <v>480</v>
+      </c>
+      <c r="L28" s="3">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="M28" s="1">
+        <v>19.52</v>
+      </c>
+      <c r="N28" s="2">
+        <f>(1 + M28)^(1/28) - 1</f>
+        <v>0.11394430370629771</v>
+      </c>
+      <c r="O28">
+        <v>0.29559999999999997</v>
+      </c>
+      <c r="P28">
+        <v>8.7800000000000003E-2</v>
+      </c>
+      <c r="Q28">
+        <v>0.25240000000000001</v>
+      </c>
+      <c r="R28">
+        <v>-5.5800000000000002E-2</v>
+      </c>
+      <c r="S28">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="T28">
+        <v>0.53059999999999996</v>
+      </c>
+      <c r="U28">
+        <v>0.41420000000000001</v>
       </c>
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C29">
         <v>20</v>
       </c>
-      <c r="I29" s="2"/>
-      <c r="N29">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="D29">
+        <v>39</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.124</v>
+      </c>
+      <c r="F29">
+        <v>76</v>
+      </c>
+      <c r="G29">
+        <v>121</v>
+      </c>
+      <c r="H29">
+        <v>9</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="J29">
+        <v>229</v>
+      </c>
+      <c r="K29">
+        <v>431</v>
+      </c>
+      <c r="L29" s="3">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="M29" s="1">
+        <v>19.73</v>
+      </c>
+      <c r="N29" s="2">
+        <f>(1 + M29)^(1/28) - 1</f>
+        <v>0.11434945152110965</v>
+      </c>
+      <c r="O29">
+        <v>0.29430000000000001</v>
+      </c>
+      <c r="P29">
+        <v>8.7900000000000006E-2</v>
+      </c>
+      <c r="Q29">
+        <v>0.249</v>
+      </c>
+      <c r="R29">
+        <v>-5.7099999999999998E-2</v>
+      </c>
+      <c r="S29">
+        <v>7.4700000000000003E-2</v>
+      </c>
+      <c r="T29">
+        <v>0.52839999999999998</v>
+      </c>
+      <c r="U29">
+        <v>0.42030000000000001</v>
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>20</v>
       </c>
-      <c r="I30" s="2"/>
-      <c r="N30">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="D30">
+        <v>36</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.129</v>
+      </c>
+      <c r="F30">
+        <v>72</v>
+      </c>
+      <c r="G30">
+        <v>147</v>
+      </c>
+      <c r="H30">
+        <v>9</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="J30">
+        <v>200</v>
+      </c>
+      <c r="K30">
+        <v>470</v>
+      </c>
+      <c r="L30" s="3">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="M30" s="1">
+        <v>19.55</v>
+      </c>
+      <c r="N30" s="2">
+        <f>(1 + M30)^(1/28) - 1</f>
+        <v>0.11400242608774258</v>
+      </c>
+      <c r="O30">
+        <v>0.29630000000000001</v>
+      </c>
+      <c r="P30">
+        <v>8.8200000000000001E-2</v>
+      </c>
+      <c r="Q30">
+        <v>0.25290000000000001</v>
+      </c>
+      <c r="R30">
+        <v>-6.1199999999999997E-2</v>
+      </c>
+      <c r="S30">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="T30">
+        <v>0.52869999999999995</v>
+      </c>
+      <c r="U30">
+        <v>0.42170000000000002</v>
       </c>
     </row>
   </sheetData>
